--- a/docs/ValueSet-ConditionDisabilityTypeVS-TWLTC.xlsx
+++ b/docs/ValueSet-ConditionDisabilityTypeVS-TWLTC.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -28,10 +28,16 @@
     <t>http://ltc-ig.fhir.tw/ValueSet/ConditionDisabilityTypeVS-TWLTC</t>
   </si>
   <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>OID:2.25.321758608038491974232931062581721483610</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -246,7 +252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -353,20 +359,28 @@
       <c r="A13" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>27</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -385,28 +399,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -425,28 +439,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
